--- a/reports/V817_2021_2023.xlsx
+++ b/reports/V817_2021_2023.xlsx
@@ -8,8 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Daily Breakdown" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Per-Entry Detail" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Weekly Breakdown" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Daily Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Per-Entry Detail" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -679,7 +680,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-29 10:02:00</t>
+          <t>2026-06-29 19:07:00</t>
         </is>
       </c>
     </row>
@@ -1005,6 +1006,96 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Month-Week</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Signals</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Wins</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Losses</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>No-fills</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Win rate</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Trading P&amp;L</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Bonus</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Closed lots</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Net P&amp;L</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>P&amp;L %</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Equity EoW</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1106,7 +1197,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/reports/V817_2021_2023.xlsx
+++ b/reports/V817_2021_2023.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-29 19:07:00</t>
+          <t>2026-06-29 21:46:00</t>
         </is>
       </c>
     </row>

--- a/reports/V817_2021_2023.xlsx
+++ b/reports/V817_2021_2023.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:Q43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -521,6 +521,10 @@
     <col width="9" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -680,7 +684,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-29 19:07:00</t>
+          <t>2026-07-01 08:27:00</t>
         </is>
       </c>
     </row>
@@ -760,7 +764,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.00%  ($0.00)</t>
         </is>
       </c>
     </row>
@@ -989,6 +993,26 @@
       <c r="M43" s="4" t="inlineStr">
         <is>
           <t>Equity EoM</t>
+        </is>
+      </c>
+      <c r="N43" s="4" t="inlineStr">
+        <is>
+          <t>Entries</t>
+        </is>
+      </c>
+      <c r="O43" s="4" t="inlineStr">
+        <is>
+          <t>Drawdown %</t>
+        </is>
+      </c>
+      <c r="P43" s="4" t="inlineStr">
+        <is>
+          <t>Drawdown $</t>
+        </is>
+      </c>
+      <c r="Q43" s="4" t="inlineStr">
+        <is>
+          <t>Worst DD at</t>
         </is>
       </c>
     </row>
@@ -996,10 +1020,10 @@
   <mergeCells count="6">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A42:Q42"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A42:M42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1011,7 +1035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1026,6 +1050,10 @@
     <col width="9" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1087,6 +1115,26 @@
       <c r="L1" s="4" t="inlineStr">
         <is>
           <t>Equity EoW</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Entries</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Drawdown %</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Drawdown $</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Worst DD at</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1118,6 +1166,8 @@
     <col width="8" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1189,6 +1239,16 @@
       <c r="N1" s="4" t="inlineStr">
         <is>
           <t>Drawdown %</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Drawdown $</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Worst DD at</t>
         </is>
       </c>
     </row>

--- a/reports/V817_2021_2023.xlsx
+++ b/reports/V817_2021_2023.xlsx
@@ -505,11 +505,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q43"/>
+  <dimension ref="A1:Q44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
@@ -524,7 +524,7 @@
     <col width="9" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -667,63 +667,63 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Chart start</t>
+          <t>Timezones</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2021-11-01 00:00:00</t>
+          <t>chart times = EET/EEST (UTC+2/+3); feed/source dates = feed zone</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Chart end</t>
+          <t>Chart start (EET/EEST)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-01 08:27:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+          <t>2021-11-01 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Chart end (EET/EEST)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-07-01 12:56:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Overall Performance</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Final equity</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>$50,000.00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Net profit incl. bonus</t>
+          <t>Final equity</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>$50,000.00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Trading P&amp;L</t>
+          <t>Net profit incl. bonus</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -735,7 +735,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Closed-lot bonus</t>
+          <t>Trading P&amp;L</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -747,118 +747,120 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>Closed-lot bonus</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>$0.00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Max drawdown</t>
+          <t>Return</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0.00%  ($0.00)</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Signals included</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>0</v>
+          <t>Max drawdown</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0.00%  ($0.00)</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Signal wins / losses</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>0 / 0</t>
-        </is>
+          <t>Signals included</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
+          <t>Signal wins / losses</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0 / 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
           <t>Signal win rate</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Entry Outcomes</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Outcome</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>% of entries</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>Total entries</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n">
+      <c r="B32" s="3" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Risk:Reward (executed)</t>
         </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Filled entries</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>No-fill entries</t>
+          <t>Filled entries</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -868,7 +870,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Winning entries</t>
+          <t>No-fill entries</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -878,7 +880,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Losing entries</t>
+          <t>Winning entries</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -888,19 +890,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Avg planned R:R</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Losing entries</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Avg realized R</t>
+          <t>Avg planned R:R</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -912,118 +912,130 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
+          <t>Avg realized R</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
           <t>Payoff (avg win / avg loss)</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="41"/>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="42"/>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>Monthly Breakdown</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Month (feed zone)</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>Regime</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>Signals</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>Wins</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
+      <c r="E44" s="4" t="inlineStr">
         <is>
           <t>Losses</t>
         </is>
       </c>
-      <c r="F43" s="4" t="inlineStr">
+      <c r="F44" s="4" t="inlineStr">
         <is>
           <t>No-fills</t>
         </is>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G44" s="4" t="inlineStr">
         <is>
           <t>Win rate</t>
         </is>
       </c>
-      <c r="H43" s="4" t="inlineStr">
+      <c r="H44" s="4" t="inlineStr">
         <is>
           <t>Trading P&amp;L</t>
         </is>
       </c>
-      <c r="I43" s="4" t="inlineStr">
+      <c r="I44" s="4" t="inlineStr">
         <is>
           <t>Bonus</t>
         </is>
       </c>
-      <c r="J43" s="4" t="inlineStr">
+      <c r="J44" s="4" t="inlineStr">
         <is>
           <t>Closed lots</t>
         </is>
       </c>
-      <c r="K43" s="4" t="inlineStr">
+      <c r="K44" s="4" t="inlineStr">
         <is>
           <t>Net P&amp;L</t>
         </is>
       </c>
-      <c r="L43" s="4" t="inlineStr">
+      <c r="L44" s="4" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="M43" s="4" t="inlineStr">
+      <c r="M44" s="4" t="inlineStr">
         <is>
           <t>Equity EoM</t>
         </is>
       </c>
-      <c r="N43" s="4" t="inlineStr">
+      <c r="N44" s="4" t="inlineStr">
         <is>
           <t>Entries</t>
         </is>
       </c>
-      <c r="O43" s="4" t="inlineStr">
+      <c r="O44" s="4" t="inlineStr">
         <is>
           <t>Drawdown %</t>
         </is>
       </c>
-      <c r="P43" s="4" t="inlineStr">
+      <c r="P44" s="4" t="inlineStr">
         <is>
           <t>Drawdown $</t>
         </is>
       </c>
-      <c r="Q43" s="4" t="inlineStr">
-        <is>
-          <t>Worst DD at</t>
+      <c r="Q44" s="4" t="inlineStr">
+        <is>
+          <t>Worst DD at (EET/EEST)</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A42:Q42"/>
-    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A43:Q43"/>
+    <mergeCell ref="A30:C30"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A34:B34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1038,7 +1050,7 @@
   <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
@@ -1053,13 +1065,13 @@
     <col width="9" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Month-Week</t>
+          <t>Month-Week (feed zone)</t>
         </is>
       </c>
       <c r="B1" s="4" t="inlineStr">
@@ -1134,7 +1146,7 @@
       </c>
       <c r="P1" s="4" t="inlineStr">
         <is>
-          <t>Worst DD at</t>
+          <t>Worst DD at (EET/EEST)</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1164,7 @@
   <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
@@ -1167,13 +1179,13 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Date (feed zone)</t>
         </is>
       </c>
       <c r="B1" s="4" t="inlineStr">
@@ -1248,7 +1260,7 @@
       </c>
       <c r="P1" s="4" t="inlineStr">
         <is>
-          <t>Worst DD at</t>
+          <t>Worst DD at (EET/EEST)</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1279,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
@@ -1282,8 +1294,8 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
     <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
-    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
     <col width="9" customWidth="1" min="20" max="20"/>
     <col width="8" customWidth="1" min="21" max="21"/>
@@ -1334,7 +1346,7 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Date (feed zone)</t>
         </is>
       </c>
       <c r="C2" s="11" t="inlineStr">
@@ -1409,12 +1421,12 @@
       </c>
       <c r="Q2" s="13" t="inlineStr">
         <is>
-          <t>Fill Time</t>
+          <t>Fill Time (EET/EEST)</t>
         </is>
       </c>
       <c r="R2" s="13" t="inlineStr">
         <is>
-          <t>Exit Time</t>
+          <t>Exit Time (EET/EEST)</t>
         </is>
       </c>
       <c r="S2" s="13" t="inlineStr">
